--- a/gaokao-paper/教辅录入任务计划清单.xlsx
+++ b/gaokao-paper/教辅录入任务计划清单.xlsx
@@ -15,9 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阶段总览" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'批次计划'!$A$1:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'批次计划'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'题目明细'!$A$1:$M$1410</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'不录清单'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'不录清单'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'跳过清单'!$A$1:$H$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1305</v>
+        <v>1323</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>T054 等 17 个题型</t>
+          <t>T124 等 14 个题型</t>
         </is>
       </c>
       <c r="E2" s="4" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>p25~p286</t>
+          <t>p88~p366</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -809,15 +809,15 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>T389~T395</t>
+          <t>T393 等 4 个题型</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>p360~p373</t>
+          <t>p369~p387</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -832,49 +832,8 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>第03批</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>概率统计</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>T399 等 3 个题型</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>p383~p405</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>待录入</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>大题必考，含马尔科夫链</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I4"/>
+  <autoFilter ref="A1:I3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7140,70 +7099,66 @@
       <c r="M101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>不录(老高考)</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="inlineStr">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>T031</t>
         </is>
       </c>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>绝对值和均值型</t>
         </is>
       </c>
-      <c r="E102" s="7" t="inlineStr">
+      <c r="E102" s="5" t="inlineStr">
         <is>
           <t>不等式</t>
         </is>
       </c>
-      <c r="F102" s="7" t="inlineStr">
+      <c r="F102" s="5" t="inlineStr">
         <is>
           <t>不等式选讲</t>
         </is>
       </c>
-      <c r="G102" s="7" t="inlineStr">
+      <c r="G102" s="5" t="inlineStr">
         <is>
           <t>典例</t>
         </is>
       </c>
-      <c r="H102" s="7" t="inlineStr">
+      <c r="H102" s="5" t="inlineStr">
         <is>
           <t>M-T-031-E1</t>
         </is>
       </c>
-      <c r="I102" s="7" t="n">
+      <c r="I102" s="5" t="n">
         <v>421</v>
       </c>
-      <c r="J102" s="7" t="inlineStr">
+      <c r="J102" s="5" t="inlineStr">
         <is>
           <t>(1) -∞,-2
 ∪[3,+∞)；(2) 证明见解析.</t>
         </is>
       </c>
-      <c r="K102" s="7" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L102" s="7" t="inlineStr">
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L102" s="5" t="inlineStr">
         <is>
           <t>函数f x  = x - 1  + x  . (1) 求不等式f x  ≥5 的解集; (2) 已知函数f x  的最小值为t，正实数a,b,c 满足a + b + 2c = 2t, 证明: 1 a + c + 1 b + c ≥2.</t>
         </is>
       </c>
-      <c r="M102" s="7" t="inlineStr">
-        <is>
-          <t>不等式选讲（柯西/绝对值不等式），新高考不考</t>
-        </is>
-      </c>
+      <c r="M102" s="5" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -7269,70 +7224,66 @@
       <c r="M103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="7" t="inlineStr">
-        <is>
-          <t>不录(老高考)</t>
-        </is>
-      </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C104" s="7" t="inlineStr">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>T031</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr">
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>绝对值和均值型</t>
         </is>
       </c>
-      <c r="E104" s="7" t="inlineStr">
+      <c r="E104" s="5" t="inlineStr">
         <is>
           <t>不等式</t>
         </is>
       </c>
-      <c r="F104" s="7" t="inlineStr">
+      <c r="F104" s="5" t="inlineStr">
         <is>
           <t>不等式选讲</t>
         </is>
       </c>
-      <c r="G104" s="7" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H104" s="7" t="inlineStr">
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
         <is>
           <t>M-T-031-V2</t>
         </is>
       </c>
-      <c r="I104" s="7" t="n">
+      <c r="I104" s="5" t="n">
         <v>421</v>
       </c>
-      <c r="J104" s="7" t="inlineStr">
+      <c r="J104" s="5" t="inlineStr">
         <is>
           <t>(1) x 1 ≤x ≤5
 ；(2) 证明见解析.</t>
         </is>
       </c>
-      <c r="K104" s="7" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L104" s="7" t="inlineStr">
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L104" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">已知f x  = x + 1  + x - 3  . (1) 求不等式f x  ≤x + 3 的解集； (2) 若f x  的最小值为m，正实数a，b，c 满足a + b + c = m，求 证：1 a + b + 1 b + c + 1 </t>
         </is>
       </c>
-      <c r="M104" s="7" t="inlineStr">
-        <is>
-          <t>不等式选讲（柯西/绝对值不等式），新高考不考</t>
-        </is>
-      </c>
+      <c r="M104" s="5" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -12801,67 +12752,67 @@
       <c r="M191" s="5" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>待录入</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>第01批</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="A192" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
         <is>
           <t>T054</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D192" s="5" t="inlineStr">
         <is>
           <t>利用对称解决恒成立和存在型</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E192" s="5" t="inlineStr">
         <is>
           <t>函数与导数</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F192" s="5" t="inlineStr">
         <is>
           <t>对称性与周期性</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="G192" s="5" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H192" s="5" t="inlineStr">
         <is>
           <t>M-T-054-V3</t>
         </is>
       </c>
-      <c r="I192" s="2" t="n">
+      <c r="I192" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="J192" s="5" t="inlineStr">
         <is>
           <t>-
 2
 2 ,+∞</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L192" s="2" t="inlineStr">
+      <c r="K192" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L192" s="5" t="inlineStr">
         <is>
           <t>已知f(x) = 2 sin|πx| - sin|πx|，g(x) = |lnx| - 2m，若对于∀x1 ∈- 2 3 ,- 1 6  ，∃x2 ∈e-1,e2  使得f x1  ≥g x2  ，则实数m 的 取值范围是 ．</t>
         </is>
       </c>
-      <c r="M192" s="2" t="inlineStr"/>
+      <c r="M192" s="5" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
@@ -13230,65 +13181,65 @@
       <c r="M198" s="5" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>待录入</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>第01批</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="inlineStr">
         <is>
           <t>T056</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D199" s="5" t="inlineStr">
         <is>
           <t>水平线法：参变分离</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E199" s="5" t="inlineStr">
         <is>
           <t>函数与导数</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F199" s="5" t="inlineStr">
         <is>
           <t>零点与图像交点</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="inlineStr">
         <is>
           <t>M-T-056-V2</t>
         </is>
       </c>
-      <c r="I199" s="2" t="n">
+      <c r="I199" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="J199" s="2" t="inlineStr">
+      <c r="J199" s="5" t="inlineStr">
         <is>
           <t>0，1</t>
         </is>
       </c>
-      <c r="K199" s="2" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L199" s="2" t="inlineStr">
+      <c r="K199" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L199" s="5" t="inlineStr">
         <is>
           <t>已知函数f(x) = |log2x|, 0 &lt; x ≤2 1 3 x2- 8 3 x + 5, x &gt; 2  ，若函数g(x) = f (x) - m 存在四个不同的零点，则实数m 的取值范围是 .</t>
         </is>
       </c>
-      <c r="M199" s="2" t="inlineStr"/>
+      <c r="M199" s="5" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
@@ -13352,65 +13303,65 @@
       <c r="M200" s="5" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>待录入</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>第01批</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="A201" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
         <is>
           <t>T057</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="D201" s="5" t="inlineStr">
         <is>
           <t>基础图像交点法</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E201" s="5" t="inlineStr">
         <is>
           <t>函数与导数</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F201" s="5" t="inlineStr">
         <is>
           <t>零点与图像交点</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
+      <c r="G201" s="5" t="inlineStr">
         <is>
           <t>典例</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="H201" s="5" t="inlineStr">
         <is>
           <t>M-T-057-E1</t>
         </is>
       </c>
-      <c r="I201" s="2" t="n">
+      <c r="I201" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="J201" s="2" t="inlineStr">
+      <c r="J201" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K201" s="2" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L201" s="2" t="inlineStr">
+      <c r="K201" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L201" s="5" t="inlineStr">
         <is>
           <t>设函数f1(x) = log2x - 1 2  x，f2(x) = log 1 2x - 1 2  x 的零 点分别为x1,x2，则（　　）</t>
         </is>
       </c>
-      <c r="M201" s="2" t="inlineStr"/>
+      <c r="M201" s="5" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
@@ -31550,69 +31501,65 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="6" t="inlineStr">
-        <is>
-          <t>人工跳过</t>
-        </is>
-      </c>
-      <c r="B495" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C495" s="6" t="inlineStr">
+      <c r="A495" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B495" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C495" s="5" t="inlineStr">
         <is>
           <t>T145</t>
         </is>
       </c>
-      <c r="D495" s="6" t="inlineStr">
+      <c r="D495" s="5" t="inlineStr">
         <is>
           <t>多参型5：“二次”最值型</t>
         </is>
       </c>
-      <c r="E495" s="6" t="inlineStr">
+      <c r="E495" s="5" t="inlineStr">
         <is>
           <t>函数与导数</t>
         </is>
       </c>
-      <c r="F495" s="6" t="inlineStr">
+      <c r="F495" s="5" t="inlineStr">
         <is>
           <t>导数压轴小题(二)</t>
         </is>
       </c>
-      <c r="G495" s="6" t="inlineStr">
+      <c r="G495" s="5" t="inlineStr">
         <is>
           <t>典例</t>
         </is>
       </c>
-      <c r="H495" s="6" t="inlineStr">
+      <c r="H495" s="5" t="inlineStr">
         <is>
           <t>M-T-145-E1</t>
         </is>
       </c>
-      <c r="I495" s="6" t="n">
+      <c r="I495" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="J495" s="6" t="inlineStr">
+      <c r="J495" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="K495" s="6" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L495" s="6" t="inlineStr">
+      <c r="K495" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L495" s="5" t="inlineStr">
         <is>
           <t>已知函数f x  = ex- 1 2 x2+ x3，若x ∈R 时，恒有f' x  ≥ 3x2+ ax + b，则ab + b 的最大值为（　　）</t>
         </is>
       </c>
-      <c r="M495" s="6" t="inlineStr">
-        <is>
-          <t>印刷错误</t>
-        </is>
-      </c>
+      <c r="M495" s="5" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="5" t="inlineStr">
@@ -37597,65 +37544,65 @@
       <c r="M590" s="5" t="inlineStr"/>
     </row>
     <row r="591">
-      <c r="A591" s="2" t="inlineStr">
-        <is>
-          <t>待录入</t>
-        </is>
-      </c>
-      <c r="B591" s="2" t="inlineStr">
-        <is>
-          <t>第01批</t>
-        </is>
-      </c>
-      <c r="C591" s="2" t="inlineStr">
+      <c r="A591" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B591" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C591" s="5" t="inlineStr">
         <is>
           <t>T182</t>
         </is>
       </c>
-      <c r="D591" s="2" t="inlineStr">
+      <c r="D591" s="5" t="inlineStr">
         <is>
           <t>最值与范围5：绝对值型</t>
         </is>
       </c>
-      <c r="E591" s="2" t="inlineStr">
+      <c r="E591" s="5" t="inlineStr">
         <is>
           <t>三角函数</t>
         </is>
       </c>
-      <c r="F591" s="2" t="inlineStr">
+      <c r="F591" s="5" t="inlineStr">
         <is>
           <t>三角函数性质与最值</t>
         </is>
       </c>
-      <c r="G591" s="2" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H591" s="2" t="inlineStr">
+      <c r="G591" s="5" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H591" s="5" t="inlineStr">
         <is>
           <t>M-T-182-V2</t>
         </is>
       </c>
-      <c r="I591" s="2" t="n">
+      <c r="I591" s="5" t="n">
         <v>146</v>
       </c>
-      <c r="J591" s="2" t="inlineStr">
+      <c r="J591" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K591" s="2" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L591" s="2" t="inlineStr">
+      <c r="K591" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L591" s="5" t="inlineStr">
         <is>
           <t>已知函数f x  = cosx，若对任意实数x1，x2，方程f x  - f x1  + f x  - f x2  = m m ∈R  有解，方程 f x  - f x1  - f x  - f x2  = n n ∈R  也有解，则m +</t>
         </is>
       </c>
-      <c r="M591" s="2" t="inlineStr"/>
+      <c r="M591" s="5" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
@@ -55311,65 +55258,65 @@
       <c r="M876" s="5" t="inlineStr"/>
     </row>
     <row r="877">
-      <c r="A877" s="2" t="inlineStr">
-        <is>
-          <t>待录入</t>
-        </is>
-      </c>
-      <c r="B877" s="2" t="inlineStr">
-        <is>
-          <t>第01批</t>
-        </is>
-      </c>
-      <c r="C877" s="2" t="inlineStr">
+      <c r="A877" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B877" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C877" s="5" t="inlineStr">
         <is>
           <t>T257</t>
         </is>
       </c>
-      <c r="D877" s="2" t="inlineStr">
+      <c r="D877" s="5" t="inlineStr">
         <is>
           <t>特殊数列3：奇偶讨论型</t>
         </is>
       </c>
-      <c r="E877" s="2" t="inlineStr">
+      <c r="E877" s="5" t="inlineStr">
         <is>
           <t>数列</t>
         </is>
       </c>
-      <c r="F877" s="2" t="inlineStr">
+      <c r="F877" s="5" t="inlineStr">
         <is>
           <t>递推求通项</t>
         </is>
       </c>
-      <c r="G877" s="2" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H877" s="2" t="inlineStr">
+      <c r="G877" s="5" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H877" s="5" t="inlineStr">
         <is>
           <t>M-T-257-V2</t>
         </is>
       </c>
-      <c r="I877" s="2" t="n">
+      <c r="I877" s="5" t="n">
         <v>217</v>
       </c>
-      <c r="J877" s="2" t="inlineStr">
+      <c r="J877" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="K877" s="2" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L877" s="2" t="inlineStr">
+      <c r="K877" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L877" s="5" t="inlineStr">
         <is>
           <t>在数列 an  中，a 1 = a a ∈N *  ，a n+1 = 1 2 an, 若an为偶数   2019 + an, 若an为奇数   n ∈N *  ，则下列结论成立的是（　　）</t>
         </is>
       </c>
-      <c r="M877" s="2" t="inlineStr"/>
+      <c r="M877" s="5" t="inlineStr"/>
     </row>
     <row r="878">
       <c r="A878" s="5" t="inlineStr">
@@ -57083,50 +57030,50 @@
       <c r="M904" s="5" t="inlineStr"/>
     </row>
     <row r="905">
-      <c r="A905" s="2" t="inlineStr">
-        <is>
-          <t>待录入</t>
-        </is>
-      </c>
-      <c r="B905" s="2" t="inlineStr">
-        <is>
-          <t>第01批</t>
-        </is>
-      </c>
-      <c r="C905" s="2" t="inlineStr">
+      <c r="A905" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B905" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C905" s="5" t="inlineStr">
         <is>
           <t>T267</t>
         </is>
       </c>
-      <c r="D905" s="2" t="inlineStr">
+      <c r="D905" s="5" t="inlineStr">
         <is>
           <t>求和难点3：指数型裂项相消</t>
         </is>
       </c>
-      <c r="E905" s="2" t="inlineStr">
+      <c r="E905" s="5" t="inlineStr">
         <is>
           <t>数列</t>
         </is>
       </c>
-      <c r="F905" s="2" t="inlineStr">
+      <c r="F905" s="5" t="inlineStr">
         <is>
           <t>数列求和</t>
         </is>
       </c>
-      <c r="G905" s="2" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H905" s="2" t="inlineStr">
+      <c r="G905" s="5" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H905" s="5" t="inlineStr">
         <is>
           <t>M-T-267-V2</t>
         </is>
       </c>
-      <c r="I905" s="2" t="n">
+      <c r="I905" s="5" t="n">
         <v>223</v>
       </c>
-      <c r="J905" s="2" t="inlineStr">
+      <c r="J905" s="5" t="inlineStr">
         <is>
           <t>(1)an= 2n；(2)Tn=
 2n- 1
@@ -57134,17 +57081,17 @@
 .</t>
         </is>
       </c>
-      <c r="K905" s="2" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L905" s="2" t="inlineStr">
+      <c r="K905" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L905" s="5" t="inlineStr">
         <is>
           <t>已知等比数列an  的前n 项和为Sn，且S4 = 30，a2，a4 的等差 中项为10. (1) 求数列an  的通项公式； (2) 求Tn= 2 S1S2 + 22 S2S3 +⋅⋅⋅+ 2n SnSn+1 .</t>
         </is>
       </c>
-      <c r="M905" s="2" t="inlineStr"/>
+      <c r="M905" s="5" t="inlineStr"/>
     </row>
     <row r="906">
       <c r="A906" s="5" t="inlineStr">
@@ -57210,50 +57157,50 @@
       <c r="M906" s="5" t="inlineStr"/>
     </row>
     <row r="907">
-      <c r="A907" s="2" t="inlineStr">
-        <is>
-          <t>待录入</t>
-        </is>
-      </c>
-      <c r="B907" s="2" t="inlineStr">
-        <is>
-          <t>第01批</t>
-        </is>
-      </c>
-      <c r="C907" s="2" t="inlineStr">
+      <c r="A907" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B907" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C907" s="5" t="inlineStr">
         <is>
           <t>T268</t>
         </is>
       </c>
-      <c r="D907" s="2" t="inlineStr">
+      <c r="D907" s="5" t="inlineStr">
         <is>
           <t>求和难点4：指数等差型裂项相消</t>
         </is>
       </c>
-      <c r="E907" s="2" t="inlineStr">
+      <c r="E907" s="5" t="inlineStr">
         <is>
           <t>数列</t>
         </is>
       </c>
-      <c r="F907" s="2" t="inlineStr">
+      <c r="F907" s="5" t="inlineStr">
         <is>
           <t>数列求和</t>
         </is>
       </c>
-      <c r="G907" s="2" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H907" s="2" t="inlineStr">
+      <c r="G907" s="5" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H907" s="5" t="inlineStr">
         <is>
           <t>M-T-268-V2</t>
         </is>
       </c>
-      <c r="I907" s="2" t="n">
+      <c r="I907" s="5" t="n">
         <v>224</v>
       </c>
-      <c r="J907" s="2" t="inlineStr">
+      <c r="J907" s="5" t="inlineStr">
         <is>
           <t>(I)an= n，bn=
 1
@@ -57263,17 +57210,17 @@
 ；(ⅱ) 证明见解析.</t>
         </is>
       </c>
-      <c r="K907" s="2" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L907" s="2" t="inlineStr">
+      <c r="K907" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L907" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">设{an} 是等差数列，{bn} 是等比数列，公比大于0．已知b1 = 1，b2+ 2b3= 1，(a2+ a6)b4= 1，a4b2= a5- a3． (I) 求数列{an}，{bn} 的通项公式；(II) 设cn= 1 + 1 n(n </t>
         </is>
       </c>
-      <c r="M907" s="2" t="inlineStr"/>
+      <c r="M907" s="5" t="inlineStr"/>
     </row>
     <row r="908">
       <c r="A908" s="5" t="inlineStr">
@@ -57987,65 +57934,65 @@
       <c r="M918" s="5" t="inlineStr"/>
     </row>
     <row r="919">
-      <c r="A919" s="2" t="inlineStr">
-        <is>
-          <t>待录入</t>
-        </is>
-      </c>
-      <c r="B919" s="2" t="inlineStr">
-        <is>
-          <t>第01批</t>
-        </is>
-      </c>
-      <c r="C919" s="2" t="inlineStr">
+      <c r="A919" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B919" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C919" s="5" t="inlineStr">
         <is>
           <t>T274</t>
         </is>
       </c>
-      <c r="D919" s="2" t="inlineStr">
+      <c r="D919" s="5" t="inlineStr">
         <is>
           <t>求和难点10：先放缩后裂项</t>
         </is>
       </c>
-      <c r="E919" s="2" t="inlineStr">
+      <c r="E919" s="5" t="inlineStr">
         <is>
           <t>数列</t>
         </is>
       </c>
-      <c r="F919" s="2" t="inlineStr">
+      <c r="F919" s="5" t="inlineStr">
         <is>
           <t>数列求和</t>
         </is>
       </c>
-      <c r="G919" s="2" t="inlineStr">
+      <c r="G919" s="5" t="inlineStr">
         <is>
           <t>典例</t>
         </is>
       </c>
-      <c r="H919" s="2" t="inlineStr">
+      <c r="H919" s="5" t="inlineStr">
         <is>
           <t>M-T-274-E1</t>
         </is>
       </c>
-      <c r="I919" s="2" t="n">
+      <c r="I919" s="5" t="n">
         <v>227</v>
       </c>
-      <c r="J919" s="2" t="inlineStr">
+      <c r="J919" s="5" t="inlineStr">
         <is>
           <t>(1)an= 22n-1；bn= 2n - 1；(2) 证明见解析.</t>
         </is>
       </c>
-      <c r="K919" s="2" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L919" s="2" t="inlineStr">
+      <c r="K919" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L919" s="5" t="inlineStr">
         <is>
           <t>已知数列an  的前n 项和为Sn，a1= 2，且对任意正整数 n，都有an+1 = 3Sn + 2，数列bn  满足bn = log2an．(1) 求数列 an  ，bn  的通项公式；(2) 求证：1 b2 1 + 1 b2 2 +⋯+</t>
         </is>
       </c>
-      <c r="M919" s="2" t="inlineStr"/>
+      <c r="M919" s="5" t="inlineStr"/>
     </row>
     <row r="920">
       <c r="A920" s="5" t="inlineStr">
@@ -76090,69 +76037,65 @@
       <c r="M1207" s="5" t="inlineStr"/>
     </row>
     <row r="1208">
-      <c r="A1208" s="6" t="inlineStr">
-        <is>
-          <t>人工跳过</t>
-        </is>
-      </c>
-      <c r="B1208" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C1208" s="6" t="inlineStr">
+      <c r="A1208" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B1208" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C1208" s="5" t="inlineStr">
         <is>
           <t>T361</t>
         </is>
       </c>
-      <c r="D1208" s="6" t="inlineStr">
+      <c r="D1208" s="5" t="inlineStr">
         <is>
           <t>坐标运算</t>
         </is>
       </c>
-      <c r="E1208" s="6" t="inlineStr">
+      <c r="E1208" s="5" t="inlineStr">
         <is>
           <t>解析几何</t>
         </is>
       </c>
-      <c r="F1208" s="6" t="inlineStr">
+      <c r="F1208" s="5" t="inlineStr">
         <is>
           <t>圆锥曲线技巧型</t>
         </is>
       </c>
-      <c r="G1208" s="6" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H1208" s="6" t="inlineStr">
+      <c r="G1208" s="5" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H1208" s="5" t="inlineStr">
         <is>
           <t>M-T-361-V1</t>
         </is>
       </c>
-      <c r="I1208" s="6" t="n">
+      <c r="I1208" s="5" t="n">
         <v>341</v>
       </c>
-      <c r="J1208" s="6" t="inlineStr">
+      <c r="J1208" s="5" t="inlineStr">
         <is>
           <t>(1)a ± 1；(2) 存在，a =-2．</t>
         </is>
       </c>
-      <c r="K1208" s="6" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L1208" s="6" t="inlineStr">
+      <c r="K1208" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L1208" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">设直线l：y = ax + 1 与双曲线C ：3x2 - y2 = 1 相交于A，B 两  点，O 为坐标原点． (1)a 为何值时，以AB 为直径的圆过原点？ (2) 是否存在实数a，使|OA  | = |OB  | 且OA  + OB </t>
         </is>
       </c>
-      <c r="M1208" s="6" t="inlineStr">
-        <is>
-          <t>答案存疑</t>
-        </is>
-      </c>
+      <c r="M1208" s="5" t="inlineStr"/>
     </row>
     <row r="1209">
       <c r="A1209" s="5" t="inlineStr">
@@ -82662,7 +82605,7 @@
       </c>
       <c r="B1314" s="2" t="inlineStr">
         <is>
-          <t>第02批</t>
+          <t>第01批</t>
         </is>
       </c>
       <c r="C1314" s="2" t="inlineStr">
@@ -82717,67 +82660,67 @@
       <c r="M1314" s="2" t="inlineStr"/>
     </row>
     <row r="1315">
-      <c r="A1315" s="2" t="inlineStr">
-        <is>
-          <t>待录入</t>
-        </is>
-      </c>
-      <c r="B1315" s="2" t="inlineStr">
-        <is>
-          <t>第02批</t>
-        </is>
-      </c>
-      <c r="C1315" s="2" t="inlineStr">
+      <c r="A1315" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B1315" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C1315" s="5" t="inlineStr">
         <is>
           <t>T389</t>
         </is>
       </c>
-      <c r="D1315" s="2" t="inlineStr">
+      <c r="D1315" s="5" t="inlineStr">
         <is>
           <t>线性回归</t>
         </is>
       </c>
-      <c r="E1315" s="2" t="inlineStr">
+      <c r="E1315" s="5" t="inlineStr">
         <is>
           <t>概率统计</t>
         </is>
       </c>
-      <c r="F1315" s="2" t="inlineStr">
+      <c r="F1315" s="5" t="inlineStr">
         <is>
           <t>回归与残差</t>
         </is>
       </c>
-      <c r="G1315" s="2" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H1315" s="2" t="inlineStr">
+      <c r="G1315" s="5" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H1315" s="5" t="inlineStr">
         <is>
           <t>M-T-389-V1</t>
         </is>
       </c>
-      <c r="I1315" s="2" t="n">
+      <c r="I1315" s="5" t="n">
         <v>360</v>
       </c>
-      <c r="J1315" s="2" t="inlineStr">
+      <c r="J1315" s="5" t="inlineStr">
         <is>
           <t>(1) 相关系数r ≈0.99，线性回归模型能够很好地拟合y 与x 的关系；y= 75
 14 x + 151
 7 ；(2)9.04 万元．</t>
         </is>
       </c>
-      <c r="K1315" s="2" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L1315" s="2" t="inlineStr">
+      <c r="K1315" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L1315" s="5" t="inlineStr">
         <is>
           <t>2020 年全面建成小康社会取得伟大历史成就，决战脱贫攻坚取得决定性胜利．某市积极探索区域特色经济，引导商家利用多媒体的优 势，对本地特产进行广告宣传，取得了社会效益和经济效益的双丰收，某商家统计了7 个月的月广告投入x(单位：万元) 与月</t>
         </is>
       </c>
-      <c r="M1315" s="2" t="inlineStr"/>
+      <c r="M1315" s="5" t="inlineStr"/>
     </row>
     <row r="1316">
       <c r="A1316" s="2" t="inlineStr">
@@ -82787,7 +82730,7 @@
       </c>
       <c r="B1316" s="2" t="inlineStr">
         <is>
-          <t>第02批</t>
+          <t>第01批</t>
         </is>
       </c>
       <c r="C1316" s="2" t="inlineStr">
@@ -82850,7 +82793,7 @@
       </c>
       <c r="B1317" s="2" t="inlineStr">
         <is>
-          <t>第02批</t>
+          <t>第01批</t>
         </is>
       </c>
       <c r="C1317" s="2" t="inlineStr">
@@ -82912,7 +82855,7 @@
       </c>
       <c r="B1318" s="2" t="inlineStr">
         <is>
-          <t>第02批</t>
+          <t>第01批</t>
         </is>
       </c>
       <c r="C1318" s="2" t="inlineStr">
@@ -82974,7 +82917,7 @@
       </c>
       <c r="B1319" s="2" t="inlineStr">
         <is>
-          <t>第02批</t>
+          <t>第01批</t>
         </is>
       </c>
       <c r="C1319" s="2" t="inlineStr">
@@ -83028,50 +82971,50 @@
       <c r="M1319" s="2" t="inlineStr"/>
     </row>
     <row r="1320">
-      <c r="A1320" s="2" t="inlineStr">
-        <is>
-          <t>待录入</t>
-        </is>
-      </c>
-      <c r="B1320" s="2" t="inlineStr">
-        <is>
-          <t>第02批</t>
-        </is>
-      </c>
-      <c r="C1320" s="2" t="inlineStr">
+      <c r="A1320" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B1320" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C1320" s="5" t="inlineStr">
         <is>
           <t>T391</t>
         </is>
       </c>
-      <c r="D1320" s="2" t="inlineStr">
+      <c r="D1320" s="5" t="inlineStr">
         <is>
           <t>剔除数据重新计算</t>
         </is>
       </c>
-      <c r="E1320" s="2" t="inlineStr">
+      <c r="E1320" s="5" t="inlineStr">
         <is>
           <t>概率统计</t>
         </is>
       </c>
-      <c r="F1320" s="2" t="inlineStr">
+      <c r="F1320" s="5" t="inlineStr">
         <is>
           <t>回归与残差</t>
         </is>
       </c>
-      <c r="G1320" s="2" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H1320" s="2" t="inlineStr">
+      <c r="G1320" s="5" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H1320" s="5" t="inlineStr">
         <is>
           <t>M-T-391-V1</t>
         </is>
       </c>
-      <c r="I1320" s="2" t="n">
+      <c r="I1320" s="5" t="n">
         <v>363</v>
       </c>
-      <c r="J1320" s="2" t="inlineStr">
+      <c r="J1320" s="5" t="inlineStr">
         <is>
           <t>(1) 填表见解析;R2≈0.90;(2)y= 0.675x - 55.9.
 (1) 由表中的数据可求出线性回归方程为y= 0.8x - 75.9，进而可完善所给表格，求出所有残差值. 由R2= 1 -
@@ -83100,78 +83043,78 @@
 ，a= y' - bx进而可求出线性回归方程.</t>
         </is>
       </c>
-      <c r="K1320" s="2" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L1320" s="2" t="inlineStr">
+      <c r="K1320" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L1320" s="5" t="inlineStr">
         <is>
           <t>BMI 指数是用体重公斤数除以身高米数的平方得出的数值，是国际上常用的衡量人体胖瘦程度以及是否健康的一个标准. 对于高中男 体育特长生而言，当BMI 数值大于或等于20.5 时，我们说体重较重，当BMI 数值小于20.5 时，我们说体重较轻</t>
         </is>
       </c>
-      <c r="M1320" s="2" t="inlineStr"/>
+      <c r="M1320" s="5" t="inlineStr"/>
     </row>
     <row r="1321">
-      <c r="A1321" s="2" t="inlineStr">
-        <is>
-          <t>待录入</t>
-        </is>
-      </c>
-      <c r="B1321" s="2" t="inlineStr">
-        <is>
-          <t>第02批</t>
-        </is>
-      </c>
-      <c r="C1321" s="2" t="inlineStr">
+      <c r="A1321" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B1321" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C1321" s="5" t="inlineStr">
         <is>
           <t>T391</t>
         </is>
       </c>
-      <c r="D1321" s="2" t="inlineStr">
+      <c r="D1321" s="5" t="inlineStr">
         <is>
           <t>剔除数据重新计算</t>
         </is>
       </c>
-      <c r="E1321" s="2" t="inlineStr">
+      <c r="E1321" s="5" t="inlineStr">
         <is>
           <t>概率统计</t>
         </is>
       </c>
-      <c r="F1321" s="2" t="inlineStr">
+      <c r="F1321" s="5" t="inlineStr">
         <is>
           <t>回归与残差</t>
         </is>
       </c>
-      <c r="G1321" s="2" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H1321" s="2" t="inlineStr">
+      <c r="G1321" s="5" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H1321" s="5" t="inlineStr">
         <is>
           <t>M-T-391-V2</t>
         </is>
       </c>
-      <c r="I1321" s="2" t="n">
+      <c r="I1321" s="5" t="n">
         <v>363</v>
       </c>
-      <c r="J1321" s="2" t="inlineStr">
+      <c r="J1321" s="5" t="inlineStr">
         <is>
           <t>(1) 见解析(2)y= 0.64x + 1.52</t>
         </is>
       </c>
-      <c r="K1321" s="2" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L1321" s="2" t="inlineStr">
+      <c r="K1321" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L1321" s="5" t="inlineStr">
         <is>
           <t>某手机公司生产某款手机，如果年返修率不超过千分之一，则生产部门当年考核优秀，现获得该公司2010 - 2018 年的相关数据如下表 所示： 年份 2010 2011 2012 2013 2014 2015 2016 2017 2018 年生</t>
         </is>
       </c>
-      <c r="M1321" s="2" t="inlineStr"/>
+      <c r="M1321" s="5" t="inlineStr"/>
     </row>
     <row r="1322">
       <c r="A1322" s="2" t="inlineStr">
@@ -83181,7 +83124,7 @@
       </c>
       <c r="B1322" s="2" t="inlineStr">
         <is>
-          <t>第02批</t>
+          <t>第01批</t>
         </is>
       </c>
       <c r="C1322" s="2" t="inlineStr">
@@ -83242,7 +83185,7 @@
       </c>
       <c r="B1323" s="2" t="inlineStr">
         <is>
-          <t>第02批</t>
+          <t>第01批</t>
         </is>
       </c>
       <c r="C1323" s="2" t="inlineStr">
@@ -83303,7 +83246,7 @@
       </c>
       <c r="B1324" s="2" t="inlineStr">
         <is>
-          <t>第02批</t>
+          <t>第01批</t>
         </is>
       </c>
       <c r="C1324" s="2" t="inlineStr">
@@ -83797,50 +83740,50 @@
       <c r="M1331" s="2" t="inlineStr"/>
     </row>
     <row r="1332">
-      <c r="A1332" s="2" t="inlineStr">
-        <is>
-          <t>待录入</t>
-        </is>
-      </c>
-      <c r="B1332" s="2" t="inlineStr">
-        <is>
-          <t>第02批</t>
-        </is>
-      </c>
-      <c r="C1332" s="2" t="inlineStr">
+      <c r="A1332" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B1332" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C1332" s="5" t="inlineStr">
         <is>
           <t>T395</t>
         </is>
       </c>
-      <c r="D1332" s="2" t="inlineStr">
+      <c r="D1332" s="5" t="inlineStr">
         <is>
           <t>非线性回归4：其他函数型</t>
         </is>
       </c>
-      <c r="E1332" s="2" t="inlineStr">
+      <c r="E1332" s="5" t="inlineStr">
         <is>
           <t>概率统计</t>
         </is>
       </c>
-      <c r="F1332" s="2" t="inlineStr">
+      <c r="F1332" s="5" t="inlineStr">
         <is>
           <t>回归与残差</t>
         </is>
       </c>
-      <c r="G1332" s="2" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H1332" s="2" t="inlineStr">
+      <c r="G1332" s="5" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H1332" s="5" t="inlineStr">
         <is>
           <t>M-T-395-V1</t>
         </is>
       </c>
-      <c r="I1332" s="2" t="n">
+      <c r="I1332" s="5" t="n">
         <v>373</v>
       </c>
-      <c r="J1332" s="2" t="inlineStr">
+      <c r="J1332" s="5" t="inlineStr">
         <is>
           <t>(1) 3
 4 ；(2)b= 0.1，a= 5.4；(3) 3
@@ -83851,17 +83794,17 @@
 100.</t>
         </is>
       </c>
-      <c r="K1332" s="2" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L1332" s="2" t="inlineStr">
+      <c r="K1332" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L1332" s="5" t="inlineStr">
         <is>
           <t>2021 年11 月4 日，第四届中国国际进口博览会在上海开幕，共计2900 多家参展商参展，420 多项新产品，新技术，新服务在本届进博会 上亮相．某投资公司现从中选出20 种新产品进行投资．为给下一年度投资提供决策依据，需了解年研发经费</t>
         </is>
       </c>
-      <c r="M1332" s="2" t="inlineStr"/>
+      <c r="M1332" s="5" t="inlineStr"/>
     </row>
     <row r="1333">
       <c r="A1333" s="2" t="inlineStr">
@@ -84657,50 +84600,50 @@
       <c r="M1343" s="5" t="inlineStr"/>
     </row>
     <row r="1344">
-      <c r="A1344" s="2" t="inlineStr">
-        <is>
-          <t>待录入</t>
-        </is>
-      </c>
-      <c r="B1344" s="2" t="inlineStr">
-        <is>
-          <t>第03批</t>
-        </is>
-      </c>
-      <c r="C1344" s="2" t="inlineStr">
+      <c r="A1344" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B1344" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C1344" s="5" t="inlineStr">
         <is>
           <t>T399</t>
         </is>
       </c>
-      <c r="D1344" s="2" t="inlineStr">
+      <c r="D1344" s="5" t="inlineStr">
         <is>
           <t>药物试验模式</t>
         </is>
       </c>
-      <c r="E1344" s="2" t="inlineStr">
+      <c r="E1344" s="5" t="inlineStr">
         <is>
           <t>概率统计</t>
         </is>
       </c>
-      <c r="F1344" s="2" t="inlineStr">
+      <c r="F1344" s="5" t="inlineStr">
         <is>
           <t>概率压轴大题</t>
         </is>
       </c>
-      <c r="G1344" s="2" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H1344" s="2" t="inlineStr">
+      <c r="G1344" s="5" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H1344" s="5" t="inlineStr">
         <is>
           <t>M-T-399-V1</t>
         </is>
       </c>
-      <c r="I1344" s="2" t="n">
+      <c r="I1344" s="5" t="n">
         <v>383</v>
       </c>
-      <c r="J1344" s="2" t="inlineStr">
+      <c r="J1344" s="5" t="inlineStr">
         <is>
           <t>(1)p = 1 -
 1
@@ -84709,17 +84652,17 @@
 k(2) (i) 证明见解析；(ii)4</t>
         </is>
       </c>
-      <c r="K1344" s="2" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L1344" s="2" t="inlineStr">
+      <c r="K1344" s="5" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L1344" s="5" t="inlineStr">
         <is>
           <t>冠状病毒是一个大型病毒家族，已知可引起感冒以及中东呼吸综合征(MERS) 和严重急性呼吸综合征(SARS) 等较严重疾病. 而今年 出现在湖北武汉的新型冠状病毒(nCoV) 是以前从未在人体中发现的冠状病毒新毒株. 人感染了新型冠状病毒后常</t>
         </is>
       </c>
-      <c r="M1344" s="2" t="inlineStr"/>
+      <c r="M1344" s="5" t="inlineStr"/>
     </row>
     <row r="1345">
       <c r="A1345" s="5" t="inlineStr">
@@ -85120,7 +85063,7 @@
       </c>
       <c r="B1351" s="2" t="inlineStr">
         <is>
-          <t>第03批</t>
+          <t>第02批</t>
         </is>
       </c>
       <c r="C1351" s="2" t="inlineStr">
@@ -87882,66 +87825,66 @@
       <c r="M1395" s="5" t="inlineStr"/>
     </row>
     <row r="1396">
-      <c r="A1396" s="2" t="inlineStr">
-        <is>
-          <t>待录入</t>
-        </is>
-      </c>
-      <c r="B1396" s="2" t="inlineStr">
-        <is>
-          <t>第03批</t>
-        </is>
-      </c>
-      <c r="C1396" s="2" t="inlineStr">
+      <c r="A1396" s="5" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B1396" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C1396" s="5" t="inlineStr">
         <is>
           <t>T415</t>
         </is>
       </c>
-      <c r="D1396" s="2" t="inlineStr">
+      <c r="D1396" s="5" t="inlineStr">
         <is>
           <t>圆锥曲线中的几何概型</t>
         </is>
       </c>
-      <c r="E1396" s="2" t="inlineStr">
+      <c r="E1396" s="5" t="inlineStr">
         <is>
           <t>概率统计</t>
         </is>
       </c>
-      <c r="F1396" s="2" t="inlineStr">
+      <c r="F1396" s="5" t="inlineStr">
         <is>
           <t>概率小题</t>
         </is>
       </c>
-      <c r="G1396" s="2" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H1396" s="2" t="inlineStr">
+      <c r="G1396" s="5" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H1396" s="5" t="inlineStr">
         <is>
           <t>M-T-415-V2</t>
         </is>
       </c>
-      <c r="I1396" s="2" t="n">
+      <c r="I1396" s="5" t="n">
         <v>405</v>
       </c>
-      <c r="J1396" s="2" t="inlineStr">
+      <c r="J1396" s="5" t="inlineStr">
         <is>
           <t>3
 4</t>
         </is>
       </c>
-      <c r="K1396" s="2" t="inlineStr">
+      <c r="K1396" s="5" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="L1396" s="2" t="inlineStr">
+      <c r="L1396" s="5" t="inlineStr">
         <is>
           <t>已知直线y = k x + 1 4  与曲线y = x 恰有两个不同的交点， 记k 的所有可能取值构成集合A，P(x,y) 是椭圆x2 16 + y2 9 = 1 上一动点，点P1(x 1,y 1) 与点P 关于直线y = x + 1 对称</t>
         </is>
       </c>
-      <c r="M1396" s="2" t="inlineStr"/>
+      <c r="M1396" s="5" t="inlineStr"/>
     </row>
     <row r="1397">
       <c r="A1397" s="5" t="inlineStr">
@@ -88865,7 +88808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -88917,112 +88860,40 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>M-T-031-E1</t>
+          <t>M-T-069-V1</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>T031</t>
+          <t>T069</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>绝对值和均值型</t>
+          <t>一元二次复合型(老高考)：线性规划型</t>
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>421</v>
+        <v>44</v>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>(1) -∞,-2
-∪[3,+∞)；(2) 证明见解析.</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>不等式选讲（柯西/绝对值不等式），新高考不考</t>
+          <t>题型名标注为老高考内容</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>函数f x  = x - 1  + x  . (1) 求不等式f x  ≥5 的解集; (2) 已知函数f x  的最小值为t，正实数a,b,c 满足a + b + 2c = 2t, 证明: 1 a + c + 1 b + c ≥2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>M-T-031-V2</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>T031</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>绝对值和均值型</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>421</v>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>(1) x 1 ≤x ≤5
-；(2) 证明见解析.</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>不等式选讲（柯西/绝对值不等式），新高考不考</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已知f x  = x + 1  + x - 3  . (1) 求不等式f x  ≤x + 3 的解集； (2) 若f x  的最小值为m，正实数a，b，c 满足a + b + c = m，求 证：1 a + b + 1 b + c + 1 </t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>M-T-069-V1</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>T069</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>一元二次复合型(老高考)：线性规划型</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>题型名标注为老高考内容</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
           <t>已知函数 f(x) = {2x+ 1,x &lt; 0 1 2 x2- 2x + 1  ,x ≥0 ，方程f 2(x) - af(x) + b = 0(b ≠ 0) 有六个不同的实数解，则3a + b 的取值范围是（　　）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -91367,7 +91238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -91416,7 +91287,7 @@
         </is>
       </c>
       <c r="C2" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D2" s="8" t="n">
         <v>1</v>
@@ -91439,7 +91310,7 @@
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>0</v>
@@ -91476,7 +91347,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>数列</t>
+          <t>概率统计</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -91485,54 +91356,31 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>递推+求和，套路明确</t>
+          <t>大题必考，含马尔科夫链</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>概率统计</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="D6" s="8" t="n">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr"/>
+      <c r="C6" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>大题必考，含马尔科夫链</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/gaokao-paper/教辅录入任务计划清单.xlsx
+++ b/gaokao-paper/教辅录入任务计划清单.xlsx
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -20613,69 +20613,65 @@
       <c r="M320" s="4" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="5" t="inlineStr">
-        <is>
-          <t>重复跳过</t>
-        </is>
-      </c>
-      <c r="B321" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C321" s="5" t="inlineStr">
+      <c r="A321" s="4" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B321" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C321" s="4" t="inlineStr">
         <is>
           <t>T093</t>
         </is>
       </c>
-      <c r="D321" s="5" t="inlineStr">
+      <c r="D321" s="4" t="inlineStr">
         <is>
           <t>切线的应用：距离公式转化型</t>
         </is>
       </c>
-      <c r="E321" s="5" t="inlineStr">
+      <c r="E321" s="4" t="inlineStr">
         <is>
           <t>函数与导数</t>
         </is>
       </c>
-      <c r="F321" s="5" t="inlineStr">
+      <c r="F321" s="4" t="inlineStr">
         <is>
           <t>导数切线与公切线</t>
         </is>
       </c>
-      <c r="G321" s="5" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H321" s="5" t="inlineStr">
+      <c r="G321" s="4" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H321" s="4" t="inlineStr">
         <is>
           <t>M-T-093-V1</t>
         </is>
       </c>
-      <c r="I321" s="5" t="n">
+      <c r="I321" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="J321" s="5" t="inlineStr">
+      <c r="J321" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K321" s="5" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L321" s="5" t="inlineStr">
+      <c r="K321" s="4" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L321" s="4" t="inlineStr">
         <is>
           <t>若x1,x2∈R，则x1- ex2  2+ x2- ex1  2的最小值是（　　）</t>
         </is>
       </c>
-      <c r="M321" s="5" t="inlineStr">
-        <is>
-          <t>与 M-T-093-E1 同题</t>
-        </is>
-      </c>
+      <c r="M321" s="4" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
@@ -37093,69 +37089,65 @@
       <c r="M584" s="4" t="inlineStr"/>
     </row>
     <row r="585">
-      <c r="A585" s="5" t="inlineStr">
-        <is>
-          <t>人工跳过</t>
-        </is>
-      </c>
-      <c r="B585" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C585" s="5" t="inlineStr">
+      <c r="A585" s="4" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B585" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C585" s="4" t="inlineStr">
         <is>
           <t>T181</t>
         </is>
       </c>
-      <c r="D585" s="5" t="inlineStr">
+      <c r="D585" s="4" t="inlineStr">
         <is>
           <t>最值与范围4：分式型</t>
         </is>
       </c>
-      <c r="E585" s="5" t="inlineStr">
+      <c r="E585" s="4" t="inlineStr">
         <is>
           <t>三角函数</t>
         </is>
       </c>
-      <c r="F585" s="5" t="inlineStr">
+      <c r="F585" s="4" t="inlineStr">
         <is>
           <t>三角函数性质与最值</t>
         </is>
       </c>
-      <c r="G585" s="5" t="inlineStr">
+      <c r="G585" s="4" t="inlineStr">
         <is>
           <t>典例</t>
         </is>
       </c>
-      <c r="H585" s="5" t="inlineStr">
+      <c r="H585" s="4" t="inlineStr">
         <is>
           <t>M-T-181-E1</t>
         </is>
       </c>
-      <c r="I585" s="5" t="n">
+      <c r="I585" s="4" t="n">
         <v>146</v>
       </c>
-      <c r="J585" s="5" t="inlineStr">
+      <c r="J585" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K585" s="5" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L585" s="5" t="inlineStr">
+      <c r="K585" s="4" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L585" s="4" t="inlineStr">
         <is>
           <t>函数f(x) = sinx - 1 3 - 2cosx - 2sinx (x ∈[0,2π]) 的最小值是（　　）</t>
         </is>
       </c>
-      <c r="M585" s="5" t="inlineStr">
-        <is>
-          <t>答案存疑</t>
-        </is>
-      </c>
+      <c r="M585" s="4" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="4" t="inlineStr">
@@ -39125,69 +39117,65 @@
       <c r="M617" s="4" t="inlineStr"/>
     </row>
     <row r="618">
-      <c r="A618" s="5" t="inlineStr">
-        <is>
-          <t>人工跳过</t>
-        </is>
-      </c>
-      <c r="B618" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C618" s="5" t="inlineStr">
+      <c r="A618" s="4" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B618" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C618" s="4" t="inlineStr">
         <is>
           <t>T190</t>
         </is>
       </c>
-      <c r="D618" s="5" t="inlineStr">
+      <c r="D618" s="4" t="inlineStr">
         <is>
           <t>解三角形基础：角与对边</t>
         </is>
       </c>
-      <c r="E618" s="5" t="inlineStr">
+      <c r="E618" s="4" t="inlineStr">
         <is>
           <t>三角函数</t>
         </is>
       </c>
-      <c r="F618" s="5" t="inlineStr">
+      <c r="F618" s="4" t="inlineStr">
         <is>
           <t>解三角形小题(一)</t>
         </is>
       </c>
-      <c r="G618" s="5" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H618" s="5" t="inlineStr">
+      <c r="G618" s="4" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H618" s="4" t="inlineStr">
         <is>
           <t>M-T-190-V1</t>
         </is>
       </c>
-      <c r="I618" s="5" t="n">
+      <c r="I618" s="4" t="n">
         <v>154</v>
       </c>
-      <c r="J618" s="5" t="inlineStr">
+      <c r="J618" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K618" s="5" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L618" s="5" t="inlineStr">
+      <c r="K618" s="4" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L618" s="4" t="inlineStr">
         <is>
           <t>在△ABC 中，角A，B，C 的对边分别为a，b，c，若sin(A + C) cosB b + cosC c  = sinA sinC ，B = π 3 ，则a + c 的取值范围是（　　）</t>
         </is>
       </c>
-      <c r="M618" s="5" t="inlineStr">
-        <is>
-          <t>提取破碎</t>
-        </is>
-      </c>
+      <c r="M618" s="4" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" s="4" t="inlineStr">
@@ -43617,69 +43605,65 @@
       <c r="M690" s="4" t="inlineStr"/>
     </row>
     <row r="691">
-      <c r="A691" s="5" t="inlineStr">
-        <is>
-          <t>人工跳过</t>
-        </is>
-      </c>
-      <c r="B691" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C691" s="5" t="inlineStr">
+      <c r="A691" s="4" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B691" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C691" s="4" t="inlineStr">
         <is>
           <t>T209</t>
         </is>
       </c>
-      <c r="D691" s="5" t="inlineStr">
+      <c r="D691" s="4" t="inlineStr">
         <is>
           <t>四心3：重心</t>
         </is>
       </c>
-      <c r="E691" s="5" t="inlineStr">
+      <c r="E691" s="4" t="inlineStr">
         <is>
           <t>三角函数</t>
         </is>
       </c>
-      <c r="F691" s="5" t="inlineStr">
+      <c r="F691" s="4" t="inlineStr">
         <is>
           <t>解三角形小题(二)</t>
         </is>
       </c>
-      <c r="G691" s="5" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H691" s="5" t="inlineStr">
+      <c r="G691" s="4" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H691" s="4" t="inlineStr">
         <is>
           <t>M-T-209-V1</t>
         </is>
       </c>
-      <c r="I691" s="5" t="n">
+      <c r="I691" s="4" t="n">
         <v>172</v>
       </c>
-      <c r="J691" s="5" t="inlineStr">
+      <c r="J691" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K691" s="5" t="inlineStr">
+      <c r="K691" s="4" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="L691" s="5" t="inlineStr">
+      <c r="L691" s="4" t="inlineStr">
         <is>
           <t>已知ΔABC 的内角A，B，C 的对边分别为a，b，c，且acosB + 3asinB = c + 1，b = 1，点G 是ΔABC 的重心，且AG = 21 3 ， 则ΔABC 的面积为（　　）</t>
         </is>
       </c>
-      <c r="M691" s="5" t="inlineStr">
-        <is>
-          <t>提取破碎</t>
-        </is>
-      </c>
+      <c r="M691" s="4" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" s="4" t="inlineStr">
@@ -88723,7 +88707,7 @@
       </c>
       <c r="L1410" s="4" t="inlineStr">
         <is>
-          <t>已知函数 $f(x)=\begin{cases}x^{3}, &amp; x\leqslanta,\\ x^{2}, &amp; x&gt;a,\end{cases}$若存在实数 $b$，使函数 $g(x)=f(x)-b$ 有两个零点，则 $a$ 的取值范围是（</t>
+          <t>已知函数 $f(x)=\begin{cases}x^{3}, &amp; x\leqslant a,\\ x^{2}, &amp; x&gt;a,\end{cases}$若存在实数 $b$，使函数 $g(x)=f(x)-b$ 有两个零点，则 $a$ 的取值范围是</t>
         </is>
       </c>
       <c r="M1410" s="4" t="inlineStr">

--- a/gaokao-paper/教辅录入任务计划清单.xlsx
+++ b/gaokao-paper/教辅录入任务计划清单.xlsx
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -64300,71 +64300,67 @@
       <c r="M1023" s="4" t="inlineStr"/>
     </row>
     <row r="1024">
-      <c r="A1024" s="5" t="inlineStr">
-        <is>
-          <t>人工跳过</t>
-        </is>
-      </c>
-      <c r="B1024" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C1024" s="5" t="inlineStr">
+      <c r="A1024" s="4" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B1024" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C1024" s="4" t="inlineStr">
         <is>
           <t>T303</t>
         </is>
       </c>
-      <c r="D1024" s="5" t="inlineStr">
+      <c r="D1024" s="4" t="inlineStr">
         <is>
           <t>求异面直线所成的角</t>
         </is>
       </c>
-      <c r="E1024" s="5" t="inlineStr">
+      <c r="E1024" s="4" t="inlineStr">
         <is>
           <t>立体几何</t>
         </is>
       </c>
-      <c r="F1024" s="5" t="inlineStr">
+      <c r="F1024" s="4" t="inlineStr">
         <is>
           <t>空间角与距离</t>
         </is>
       </c>
-      <c r="G1024" s="5" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H1024" s="5" t="inlineStr">
+      <c r="G1024" s="4" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H1024" s="4" t="inlineStr">
         <is>
           <t>M-T-303-V2</t>
         </is>
       </c>
-      <c r="I1024" s="5" t="n">
+      <c r="I1024" s="4" t="n">
         <v>271</v>
       </c>
-      <c r="J1024" s="5" t="inlineStr">
+      <c r="J1024" s="4" t="inlineStr">
         <is>
           <t>π
 4 , π
 2</t>
         </is>
       </c>
-      <c r="K1024" s="5" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L1024" s="5" t="inlineStr">
+      <c r="K1024" s="4" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L1024" s="4" t="inlineStr">
         <is>
           <t>如图，已知正三棱锥A - BCD，BC = CD = BD = 3 ，AB = AC = AD = 2，点P，Q 分别棱BC，CD 上(不包含端点)，则直 线AP，BQ 所成的角的取值范围是 .</t>
         </is>
       </c>
-      <c r="M1024" s="5" t="inlineStr">
-        <is>
-          <t>答案存疑</t>
-        </is>
-      </c>
+      <c r="M1024" s="4" t="inlineStr"/>
     </row>
     <row r="1025">
       <c r="A1025" s="5" t="inlineStr">
@@ -64982,69 +64978,65 @@
       <c r="M1034" s="4" t="inlineStr"/>
     </row>
     <row r="1035">
-      <c r="A1035" s="5" t="inlineStr">
-        <is>
-          <t>人工跳过</t>
-        </is>
-      </c>
-      <c r="B1035" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C1035" s="5" t="inlineStr">
+      <c r="A1035" s="4" t="inlineStr">
+        <is>
+          <t>已录入</t>
+        </is>
+      </c>
+      <c r="B1035" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C1035" s="4" t="inlineStr">
         <is>
           <t>T306</t>
         </is>
       </c>
-      <c r="D1035" s="5" t="inlineStr">
+      <c r="D1035" s="4" t="inlineStr">
         <is>
           <t>翻折中的角度</t>
         </is>
       </c>
-      <c r="E1035" s="5" t="inlineStr">
+      <c r="E1035" s="4" t="inlineStr">
         <is>
           <t>立体几何</t>
         </is>
       </c>
-      <c r="F1035" s="5" t="inlineStr">
+      <c r="F1035" s="4" t="inlineStr">
         <is>
           <t>空间角与距离</t>
         </is>
       </c>
-      <c r="G1035" s="5" t="inlineStr">
-        <is>
-          <t>变式</t>
-        </is>
-      </c>
-      <c r="H1035" s="5" t="inlineStr">
+      <c r="G1035" s="4" t="inlineStr">
+        <is>
+          <t>变式</t>
+        </is>
+      </c>
+      <c r="H1035" s="4" t="inlineStr">
         <is>
           <t>M-T-306-V1</t>
         </is>
       </c>
-      <c r="I1035" s="5" t="n">
+      <c r="I1035" s="4" t="n">
         <v>275</v>
       </c>
-      <c r="J1035" s="5" t="inlineStr">
+      <c r="J1035" s="4" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="K1035" s="5" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="L1035" s="5" t="inlineStr">
+      <c r="K1035" s="4" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L1035" s="4" t="inlineStr">
         <is>
           <t>如图，矩形ABCD 中，已知AB = 2，BC = 4，E 为AD 的中点． 将△ABE 沿着BE 向上翻折至△ABE，记锐二面角A- BE - C 的平面角为α，AB 与平面BCDE 所成的角为β，则下列结论 不可能成立的是（　　）</t>
         </is>
       </c>
-      <c r="M1035" s="5" t="inlineStr">
-        <is>
-          <t>答案存疑</t>
-        </is>
-      </c>
+      <c r="M1035" s="4" t="inlineStr"/>
     </row>
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
@@ -89437,12 +89429,12 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>提取破碎</t>
+          <t>已补录</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>分段式 "a x - 1" 无法判定是 ax-1 / a^x-1 / x-a，三种解读都推不出原书答案 (-1,0)∪(0,+∞)</t>
+          <t>分段式 "a x - 1" 无法判定是 ax-1 / a^x-1 / x-a，三种解读都推不出原书答案 (-1,0)∪(0,+∞) | 第132批补录为 M-H1384</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -89477,12 +89469,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>提取破碎</t>
+          <t>已补录</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>t = x + 1/(4x+1) 的形式与解析"t=1 无解"矛盾，无法重建</t>
+          <t>t = x + 1/(4x+1) 的形式与解析"t=1 无解"矛盾，无法重建 | 第132批补录为 M-H1385</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -89679,12 +89671,12 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>待核查</t>
+          <t>已补录</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>需人工核对原 PDF 后决定是否补录</t>
+          <t>需人工核对原 PDF 后决定是否补录 | 第132批补录为 M-H1386</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -90163,12 +90155,12 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>答案存疑</t>
+          <t>已补录</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>原书答案 B(-1) 错误。f=(sinx-1)/(3-2cosx-2sinx)，驻点方程 cosx+2sinx-2=0 得 sinx=3/5,cosx=4/5，真实最小值 = -2；原书详解把 -(1-sinx)/[(1-sinx)^2+(1-cosx)^2] 除以 (1-sinx)^2 后丢掉因子 (1-sinx)，误得 -1。且 -2 与所见选项（A.-1/2 B.-1 C.-2 D.-3）对应 C 而非 B</t>
+          <t>原书答案 B(-1) 错误。f=(sinx-1)/(3-2cosx-2sinx)，驻点方程 cosx+2sinx-2=0 得 sinx=3/5,cosx=4/5，真实最小值 = -2；原书详解把 -(1-sinx)/[(1-sinx)^2+(1-cosx)^2] 除以 (1-sinx)^2 后丢掉因子 (1-sinx)，误得 -1。且 -2 与所见选项（A.-1/2 B.-1 C.-2 D.-3）对应 C 而非 B | 第132批补录为 M-H1387</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr"/>
@@ -90273,12 +90265,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>提取破碎</t>
+          <t>已补录</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>四个选项在 PDF 提取后全部塌成同一个「(√3/2, √3]」，无法还原四个互不相同的选项；严格推导值域为 (√3/2, √3]（B=π/3、b=√3/2 ⟹ a+c=√3 sin(A+π/6)），答案 A 可信，但选项不能凭空构造，故不录</t>
+          <t>四个选项在 PDF 提取后全部塌成同一个「(√3/2, √3]」，无法还原四个互不相同的选项；严格推导值域为 (√3/2, √3]（B=π/3、b=√3/2 ⟹ a+c=√3 sin(A+π/6)），答案 A 可信，但选项不能凭空构造，故不录 | 第132批补录为 M-H1388</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -90320,12 +90312,12 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>提取破碎</t>
+          <t>已补录</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>题干可解（A=π/3,c=4,a=√13,S=√3）但原页选项行未提取到，无法确认答案 B 对应形式。</t>
+          <t>题干可解（A=π/3,c=4,a=√13,S=√3）但原页选项行未提取到，无法确认答案 B 对应形式。 | 第132批补录为 M-H1389</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -90838,12 +90830,12 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>答案存疑</t>
+          <t>已补录</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>题设 BC=CD=BD=√3、AB=AC=AD=2 时，底面外接圆半径 1、AO=√3、tan∠APO=√3/1=√3 ⟹ ∠APO 最小为 π/3，与答案 π/4 矛盾。要得 π/4 需 AO=OB，即 BC=√6。疑原文数据有误。</t>
+          <t>题设 BC=CD=BD=√3、AB=AC=AD=2 时，底面外接圆半径 1、AO=√3、tan∠APO=√3/1=√3 ⟹ ∠APO 最小为 π/3，与答案 π/4 矛盾。要得 π/4 需 AO=OB，即 BC=√6。疑原文数据有误。 【第133批已复核补录】</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -90918,12 +90910,12 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>答案存疑</t>
+          <t>已补录</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>详解推出 sinα=A′H/OA′、sinβ=A′H/A′B，而正方形 ABFE 中 OA′=a√2/2、A′B=a，故 sinα=√2·sinβ。选项 A 写 sinα=2sinβ，疑 √2 丢根号成 2；且 B、C、D 的判定过程在页尾截断。</t>
+          <t>详解推出 sinα=A′H/OA′、sinβ=A′H/A′B，而正方形 ABFE 中 OA′=a√2/2、A′B=a，故 sinα=√2·sinβ。选项 A 写 sinα=2sinβ，疑 √2 丢根号成 2；且 B、C、D 的判定过程在页尾截断。 【第133批已复核补录】</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -91154,12 +91146,12 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>答案存疑</t>
+          <t>已补录</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>原书答「存在，a=-2」。数值检验：|OA|=|OB| 只在 a=0 成立（|OA|^2-|OB|^2=(x1-x2)·8a/(3-a^2)）；而 (y1+y2)/(x1+x2)=3/a=1/2 要求 a=6，此时 a^2=36&gt;6 使 Δ&lt;0 无交点。a=-2 时 |OA|^2=0.37、|OB|^2=45.63 两条件均不满足。严格结论应为「不存在」，与原书答案方向相反，故不录入。</t>
+          <t>原书答「存在，a=-2」。数值检验：|OA|=|OB| 只在 a=0 成立（|OA|^2-|OB|^2=(x1-x2)·8a/(3-a^2)）；而 (y1+y2)/(x1+x2)=3/a=1/2 要求 a=6，此时 a^2=36&gt;6 使 Δ&lt;0 无交点。a=-2 时 |OA|^2=0.37、|OB|^2=45.63 两条件均不满足。严格结论应为「不存在」，与原书答案方向相反，故不录入。 【第133批已复核补录】</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
